--- a/data/excel_reports/master_database.xlsx
+++ b/data/excel_reports/master_database.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -75,6 +75,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5046,6 +5047,6069 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>DMK betrayed mandate given by T.N. people in 2021, says PM Modi in Tiruchi rally</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi criticizes DMK's governance and promises better law and order under NDA</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>DMK betrayed the mandate given by the people of Tamil Nadu in 2021, according to PM Modi, PM Modi accused DMK of corruption and dynastic rule, NDA promises to maintain good law and order and ensure people live without fear</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/tamil-nadu/dmk-betrayed-mandate-given-by-tn-people-in-2021-says-pm-modi-in-tiruchi-rally/article70732236.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Speaker forced to act according to government wishes: Opposition in Lok Sabha</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Opposition moves no-confidence motion against Speaker Om Birla, alleging government interference in Lok Sabha proceedings.</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>Motion for removal of Speaker Om Birla moved in Lok Sabha, Opposition claims Speaker is being forced to act according to government wishes, Leader of Opposition Rahul Gandhi barred from speaking in the House</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/speaker-forced-to-act-according-to-government-wishes-opposition-in-lok-sabha/article70731432.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Iran police chief says anti-government protesters treated as 'enemies'</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Iran's police chief issues a warning to anti-government protesters, stating they will be treated as enemies if they support the country's foes.</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Iranian police chief warns protesters of being treated as enemies, Crackdown on anti-government protests in January, Over 3,000 deaths in the unrest</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/iran-police-chief-says-anti-government-protesters-treated-as-enemies/article70732295.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Afghan Govt says three civilians killed by Pakistani shelling</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Afghanistan and Pakistan have been engaged in cross-border clashes, resulting in civilian casualties.</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Afghanistan and Pakistan have been involved in cross-border clashes since February 26, 2026, Pakistan has fired hundreds of mortars and artillery along the border, causing civilian casualties, The Taliban government has accused Pakistan of targeting civilians</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/afghan-govt-says-three-civilians-killed-by-pakistani-shelling/article70732299.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Kremlin says Britain was involved in Ukraine’s missile strike on Russia</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Russia accuses Britain of involvement in a Ukrainian strike on a Russian city, escalating the Russia-Ukraine conflict.</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Russia accused Britain of involvement in a Ukrainian strike on a Russian city using British missiles, Kremlin said it would take Britain's role into account, Russia-Ukraine conflict continues with military operations</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/kremlin-says-britain-was-involved-in-ukraines-missile-strike-on-russia/article70732300.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>‘Targeting mistake’ led to U.S. missile strike on Iranian school: report</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>US responsible for missile strike on Iranian school due to targeting mistake, amid ongoing conflict with Iran and Israel</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>US missile strike on Iranian school due to targeting mistake, Iran-Israel conflict, US military conducting strikes on Iranian base</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/targeting-mistake-led-to-us-missile-strike-on-iranian-school-report/article70732306.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Iran’s new Supreme Leader injured but ‘safe’, officials say</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Iran's new Supreme Leader Mojtaba Khamenei is injured but safe after an air strike in the US-Israeli war against the Islamic republic.</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Iran's new Supreme Leader Mojtaba Khamenei is injured but 'safe', officials say, He was injured in an air strike at the start of the US-Israeli war against the Islamic republic, The strike also killed other members of the Khamenei family, including his wife and mother</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/irans-new-supreme-leader-mojtaba-hurt-in-strike-that-killed-his-father-report/article70731605.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Nepal's RSP gets highest number of votes under proportional representation category</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Nepal's Rastriya Swatantra Party wins highest number of votes under proportional representation category in Nepal general elections.</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Nepal's Rastriya Swatantra Party (RSP) received the highest number of votes under proportional representation category, Total 110 members are elected through proportional representation in the House of Representatives (HoR) in Nepal, RSP, Nepali Congress, CPN-UML, NCP, Shrama Sanskriti Party and Rastriya Prajatantra Party are likely to get recognition as national parties</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/nepals-rsp-gets-highest-number-of-votes-under-proportional-representation-category/article70732277.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>A supermajority for RSP leaves Nepal’s Parliament with weakest Opposition</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Nepal's Rastriya Swatantra Party secures a supermajority in the Parliament, leaving the Opposition weakened.</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Rastriya Swatantra Party (RSP) secured 182 seats in the 275-member Parliament, just two short of a two-thirds majority, Established parties such as the Nepali Congress (NC) and the CPN-UML have been reduced to 38 and 25 seats, respectively, A weak Opposition in Parliament carries risks and could test democratic norms</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/a-supermajority-for-rsp-leaves-nepals-parliament-with-weakest-opposition/article70730952.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Faunal survey in Kerala’s Vazhachal adds 26 species to checklist of wildlife division in Western Ghats</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>A faunal survey in Kerala's Vazhachal wildlife division documents 26 new species and highlights the rich biodiversity of the Western Ghats.</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Faunal survey in Kerala's Vazhachal adds 26 species to checklist of wildlife division in Western Ghats, Survey conducted by Kerala Forest department in association with Travancore Nature History Society, 175 species of butterflies recorded during the survey, including 13 new additions</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/faunal-survey-in-keralas-vazhachal-adds-26-species-to-checklist-of-wildlife-division-in-western-ghats/article70725393.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>With lunar missions looming, scientists grow chickpeas in 'moon dirt'</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Scientists have successfully grown chickpeas in simulated lunar soil, a breakthrough for future space missions and sustainable food production.</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Scientists have grown chickpeas in simulated lunar soil, a step toward enabling astronauts to produce food on long-term moon missions., The soil mixture was composed of up to 75% lunar simulant and included beneficial fungi and vermicompost., This achievement is crucial for future space missions and can have implications for sustainable food production on Earth as well.</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/science/with-lunar-missions-looming-scientists-grow-chickpeas-in-moon-dirt/article70725290.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>‘How will he speak from Germany?’: Amit Shah attacks Rahul Gandhi over foreign trips during House sessions</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Amit Shah criticizes Rahul Gandhi for his low attendance and participation in key debates, citing his frequent foreign trips during House sessions.</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips during House sessions, Lok Sabha has no provision for video conferencing, Amit Shah's attack on Rahul Gandhi's attendance and participation in key debates</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/amit-shah-rahul-gandhi-foreign-trips-parliament-10577047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Social Issues</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>With fewer than 10 Kurumba artists left, a 3,000-year tradition faces extinction</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>The Kurumba painting, a 3000-year-old art form, is at risk of extinction due to the dwindling number of indigenous practitioners.</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Kurumba painting is a 3000-year-old prehistoric art form, Only 10 indigenous practitioners remain, The art form is at risk of extinction due to low literacy levels and stagnant population</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/kurumba-artists-tradition-kotagiri-tamil-nadu-10577004/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>NCERT book row: Who are the 3 whom SC wants Centre, states to disassociate from</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Supreme Court directs Centre, states, and universities to dissociate from three members of the textbook development team.</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Supreme Court directed Centre, states, and universities to dissociate from three members of the textbook development team, NCERT Director D P Saklani mentioned the chapter was drafted by a team under Prof Michel Danino, National Syllabus and Teaching Learning Material Committee (NSTC) is an overarching committee constituted by the NCERT in 2023</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/ncert-book-row-sc-wants-centre-states-disassociate-10576984/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>BJP MP demands action against Bengal government for President’s ‘protocol breach’</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>BJP MP demands action against Bengal government for President's protocol breach, citing constitutional implications.</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Protocol breach of President Droupadi Murmu during a visit to West Bengal, BJP MP seeks action under Article 356, Union Home Ministry asked for explanation from West Bengal government</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/president-murmu-protocol-breach-bjp-mp-baburam-nishad-bengal-row-10576625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>CBI arrests own inspector for seeking Rs 2 crore to ‘settle’ complaint from South Delhi resident</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>CBI inspector arrested for allegedly trying to extort Rs 2 crore from a South Delhi resident under the guise of 'settling' a complaint.</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>CBI inspector arrested for corruption, Extortion of Rs 2 crore from a South Delhi resident, CBI's internal corruption and accountability</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/cbi-inspector-extortion-fir-south-delhi-resident-10576514/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>‘Whenever there is discussion, he seems to be abroad’: Amit Shah slams Rahul Gandhi over attendance in Lok Sabha</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Amit Shah criticizes Rahul Gandhi's attendance in Lok Sabha, highlighting the importance of parliamentary attendance.</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Amit Shah slams Rahul Gandhi over attendance in Lok Sabha, Discussion on Lok Sabha attendance is relevant to Polity and Governance, Attendance in Lok Sabha is a key aspect of parliamentary functioning</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/whenever-there-is-discussion-he-seems-to-be-abroad-amit-shah-slams-rahul-gandhi-over-attendance-in-lok-sabha/articleshow/129465284.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>INDIA bloc MPs back TMC's motion to remove CEC Gyanesh Kumar; notice likely in Parliament soon</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>TMC moves to remove CEC Gyanesh Kumar, a notice likely in Parliament soon.</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>TMC's motion to remove CEC Gyanesh Kumar, likely notice in Parliament soon, CEC is a key figure in India's electoral process</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/a-welcome-step-opposition-backs-tmcs-move-to-bring-impeachment-motion-against-cec-gyanesh-kumar/articleshow/129455884.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>India prepares for its biggest headcount: What makes Census 2027 different</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>India gears up for Census 2027, a digital headcount with caste enumeration for the first time since 1931.</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Census 2027 will include caste enumeration for the first time since 1931, Digital approach aims for efficiency and transparency, Exercise will be crucial for Lok Sabha delimitation, potentially impacting women's reservation</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/india-prepares-for-its-biggest-headcount-what-makes-census-2027-different/articleshow/129453145.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Minister urged to expedite construction work on medical colleges</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Praja Arogya Vedika urges the Minister to expedite construction work on medical colleges for the benefit of students.</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Praja Arogya Vedika (PAV) urged the Minister to expedite construction work on newly-sanctioned medical colleges, Limited additional funding and administrative action required to complete the remaining work, Government can make these colleges ready for admissions in the upcoming academic year with immediate steps</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/andhra-pradesh/minister-urged-to-expedite-construction-work-on-medical-colleges/article70731796.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ED attaches properties worth ₹1.44 crore in misappropriation of UNA funds case</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>ED attaches properties worth ₹1.44 crore in UNA funds misappropriation case</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>Misappropriation of UNA funds, Properties worth ₹1.44 crore attached by ED, Money laundering case under PMLA, 2002</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/ed-attaches-properties-worth-144-crore-in-misappropriation-of-una-funds-case/article70731380.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Parliament likely to take up Bill to codify IPS deputation in CAPFs this session</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Parliament to introduce Bill to codify IPS deputation in CAPFs in response to Supreme Court ruling.</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>Parliament to introduce Central Armed Forces (General Administration) Bill to codify IPS deputation in CAPFs, Bill in response to Supreme Court ruling to reduce IPS deputation in CAPFs, Union Cabinet approved the Bill on March 10</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/parliament-likely-to-take-up-bill-to-codify-ips-deputation-in-capfs-this-session/article70732194.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Shivaram Karanth Layout: BDA to seek court’s permission to call applications for allotment of sites</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>BDA seeks court's permission to call applications for allotment of residential sites in Shivaram Karanth Layout, citing financial losses due to delay.</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>BDA is suffering a loss of ₹1,000 crore a year due to delay in calling for applications to allot sites, ₹10,000 crore spent on formation of Shivaram Karanth Layout, BDA developing software to allocate compensatory sites to land-losing farmers</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/shivaram-karanth-layout-bda-to-seek-courts-permission-to-call-applications-for-allotment-of-sites/article70732182.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Government plans to raise income limit for post-matric scholarship for SCs, OBCs, DNTs from 26-27 onwards</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Government plans to raise income limit for post-matric scholarship and launch new schemes for SC, ST, OBC, and DNT students.</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>Raising income limit for post-matric scholarship for SCs, OBCs, DNTs from ₹2.5 lakh to ₹4.5 lakh, Launch of new scheme 'SAMRAS' for building hostels in Central universities, Revision of National Overseas Scholarship (NOS) scheme for SC students</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/government-plans-to-raise-income-limit-for-post-matric-scholarship-for-scs-obcs-dnts-from-26-27-onwards/article70731499.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court notice on plea against scheme for regularising ‘illegal’ digital advertisement hoardings</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court issues notice on a PIL petition challenging the regularization of 'illegal' digital advertisement hoardings in Bengaluru.</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court notice on plea against scheme for regularising 'illegal' digital advertisement hoardings, Rule 8(7)(vii) of the Greater Bengaluru Area (Advertisement) Rules, 2025 challenged, Government order dated February 4, 2026, provides a three-month window for conversion</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/karnataka-high-court-notice-on-plea-against-scheme-for-regularising-illegal-digital-advertisement-hoardings/article70731998.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>APSSDC, OMCAP sign MoU with Apollo MedSkills to facilitate overseas jobs for youth</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>APSSDC, OMCAP, and Apollo MedSkills collaborate to provide overseas employment opportunities for Andhra Pradesh youth in healthcare and allied sectors.</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>APSSDC, OMCAP, and Apollo MedSkills signed MoU for overseas employment opportunities for youth, 500 candidates to be trained and placed in the first phase, potential to expand to 1000 candidates, APSSDC may extend financial support of up to ₹15,000 per candidate towards training costs</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/andhra-pradesh/apssdc-omcap-sign-mou-with-apollo-medskills-to-facilitate-overseas-jobs-for-youth/article70731788.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>LPG cylinder shortage: Bengaluru hotels switch to induction, kerosene stoves</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>LPG cylinder shortage in Bengaluru forces restaurants to adopt alternative cooking methods, affecting their operations and menu options.</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>LPG cylinder shortage in Bengaluru, Restaurants switching to alternatives like kerosene stoves and induction cooktops, Impact on hotel operations and menu options</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/videos/lpg-cylinder-shortage-bengaluru-hotels-switch-to-induction-kerosene-stoves/article70732426.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Supreme Court judge distinguishes between active and passive euthanasia</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Supreme Court judge clarifies the distinction between active and passive euthanasia in a recent judgment.</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>Supreme Court judge distinguishes between active and passive euthanasia, Active euthanasia is causing death by introducing a new, external agency of harm, Passive euthanasia is allowing death to occur by withdrawing or withholding life support</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/supreme-court-judge-distinguishes-between-active-and-passive-euthanasia/article70732031.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Raichur bandh call seeking internal quota for SCs gets good response</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Raichur bandh demands internal quota for SCs and postponement of government recruitment</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Internal reservation for SCs in government jobs, State government's delay in implementation, 56,000 government posts to be filled, Madiga community and Dalit organisations participated in the protest, Demonstrators marched towards Dr. B.R. Ambedkar Circle and burned an effigy of Social Welfare Minister</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/raichur-bandh-call-seeking-internal-quota-for-scs-gets-good-response/article70731698.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>New EPS rules leave out clause on higher pension</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - National</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>The Employees' Pension Scheme (EPS)-2026 has left out a clause on higher pension, which was previously a contentious issue.</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>Employees' Pension Scheme (EPS)-2026 has left out the contentious clause on higher pension, Clause was omitted due to it being regarded as 'obsolete', Supreme Court verdict in November 2022 permitted pensioners to apply for higher pension</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/new-eps-rules-leave-out-clause-on-higher-pension/article70731399.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>U.S. has ‘practically nothing left to target’ in Iran, says Trump: report</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>US President Trump signals end of war with Iran, citing 'practically nothing left to target'</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>US-Iran war updates, Trump signals end of war, Global economic disruption, US-Israel operation against Iran</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/us-has-practically-nothing-left-to-target-in-iran-says-trump-report/article70732296.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Poland to seek help from two other countries in Epstein investigation</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Poland launches an investigation into human trafficking related to Jeffrey Epstein, seeking help from France and Sweden.</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>Poland is investigating human trafficking related to Jeffrey Epstein, with a focus on ties to Russian intelligence and offenses affecting Polish citizens., Poland will seek help from France and Sweden in the investigation., The investigation is based on documents from the Epstein files indicating a reasonable suspicion of human trafficking in Poland.</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/poland-to-seek-help-from-two-other-countries-in-epstein-investigation/article70732303.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>28 Indian vessels with 778 seafarers onboard stuck in Persian Gulf: Official</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>28 Indian vessels with 778 seafarers are stuck in the Persian Gulf, prompting the government to monitor their safety and security.</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>28 Indian vessels with 778 seafarers stuck in Persian Gulf, 24 vessels on western part of Strait of Hormuz, 4 on eastern side, Government monitoring vessels for safety and security</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/28-indian-vessels-with-778-seafarers-onboard-stuck-in-persian-gulf-official/article70731599.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>9. Defense &amp; Security</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>White House area shut down after van breaches security barricade</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>A van breached the security barricade near the White House, leading to a shutdown of the area and heightened security measures.</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>White House area shut down after van breaches security barricade, Driver taken into custody and no reported injuries, Heightened security amid U.S.-Israel war on Iran</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/white-house-area-shut-down-after-van-breaches-security-barricade/article70731188.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>India-bound Thai-flagged cargo ship attacked in Strait of Hormuz</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>A Thai cargo ship was attacked in the Strait of Hormuz, highlighting tensions in the region and potential risks to global energy supplies.</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>India-bound Thai-flagged cargo ship attacked in Strait of Hormuz, Iran has launched strikes against its oil-exporting neighbours, Threats to shipping in the Strait of Hormuz and global energy economy crisis</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/india-bound-thai-flagged-cargo-ship-attacked-in-strait-of-hormuz/article70731138.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Iran says it will target U.S.-Israeli economic, banking interests in region</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - International</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Iran threatens to target U.S.-Israeli economic interests in the region after an attack on an Iranian bank.</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>Iran plans to target U.S.-Israeli economic and banking interests in the region, Iranian bank attacked by unknown forces, Iran's military spokesperson warns of retaliation against U.S. and Israeli economic centers</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/international/iran-says-it-will-target-us-israeli-economic-banking-interests-in-region/article70730566.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>India has overall coal stock of 88 days, confident of meeting rise in power demand: Ministry</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>India has sufficient coal stock to meet rising power demand, with coal production and supply exceeding consumption.</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>India has an overall coal stock of 210 million tonnes, adequate for 88 days, Coal production and supply continue to be higher than consumption, Coal production and supply to the Non-Regulated Sector have increased by 14% compared to the previous year</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/india-has-overall-coal-stock-of-88-days-confident-of-meeting-rise-in-power-demand-ministry/article70732240.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>LPG crisis LIVE: Centre directs States to monitor LPG supply, prevent hoarding, black marketing of cylinders</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Centre directs States to monitor LPG supply and prevent hoarding and black marketing amid shortage caused by West Asia war.</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage in India due to supply chain disruptions caused by the war in West Asia, Government prioritizes domestic cooking gas supply to households, leading to a supply crunch for hotels and restaurants, States directed to monitor LPG supply and prevent hoarding and black marketing</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/lpg-crisis-india-shortage-of-commercial-lpg-live-updates-march-11-hotels-and-restaurants-hit/article70729658.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Reliance Industries seeking to maximise LPG output, divert natural gas to support priority sectors</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Reliance Industries aims to increase LPG production and divert natural gas to priority sectors as per government guidelines.</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>Reliance Industries seeking to maximise LPG output, Diverting natural gas to support priority sectors, Government invoking Essential Commodities Act, 1955</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Industry/reliance-industries-seeking-to-maximise-lpg-output-divert-natural-gas-to-support-priority-sectors/article70728151.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>How the U.S.-Israel conflict with Iran is exposing India’s LPG dependence | Data</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>India's LPG supply is affected by the US-Israel conflict with Iran, leading to higher global prices and domestic price hike</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>India's LPG supply is heavily import dependent and in need of government aid, Centre paid ₹30,000 crore to subsidise OMCs' losses for selling cooking gas, Domestic LPG prices raised by ₹60 per cylinder due to conflict and global price rise</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/data/how-the-us-israel-conflict-with-iran-is-exposing-indias-lpg-dependence/article70728126.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Stablecoins increasingly favoured for money laundering, financing of terrorism and proliferation: FATF report</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>FATF report warns of stablecoins being used for money laundering, terror financing, and proliferation financing.</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>Stablecoins are increasingly being used for money laundering and terror financing, State-linked actors in Iran and North Korea are using stablecoins for proliferation financing and weapons procurement, FATF report highlights vulnerabilities in stablecoins due to their characteristics</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/technology/stablecoins-increasingly-favoured-for-money-laundering-financing-of-terrorism-and-proliferation-fatf-report/article70708437.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Stock markets rebound tracking drop in crude oil prices, rally in global peers</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Stock markets in India rebounded due to a drop in crude oil prices and a rally in global peers.</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>Stock markets rebounded due to drop in crude oil prices and rally in global peers, Foreign Institutional Investors offloaded equities worth ₹6,345.57 crore, Sensex and Nifty ended nearly 1% higher on Tuesday</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/markets/stock-markets-rebound-tracking-drop-in-crude-oil-prices-rally-in-global-peers/article70726240.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Government seeks Lok Sabha nod for ₹2.81 lakh crore gross additional expenditure in FY26</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Government seeks Lok Sabha approval for ₹2.81 lakh crore gross additional expenditure in FY26</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>Government seeks Lok Sabha approval for gross additional expenditure of over ₹2.81 lakh crore in FY26, Net cash outgo aggregates to ₹2,01,142.96 crore and gross additional expenditure matched by savings aggregates to ₹80,145.71 crore, Union Finance Minister Nirmala Sitharaman tables Supplementary Demands for Grants in Lok Sabha</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/government-seeks-lok-sabha-nod-for-281-lakh-crore-gross-additional-expenditure-in-fy26/article70726265.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>India eases rules to allow Chinese investments to enter, sets ownership limits</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>India has relaxed its rules to allow Chinese investments to enter the country with ownership limits, amending its 2020 rule that restricted foreign direct investment from countries sharing a land border with India.</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>India has eased rules to allow Chinese investments to enter the country with ownership limits, The 2020 rule that restricted foreign direct investment from countries sharing a land border with India has been amended, The new rule allows companies with non-controlling stake belonging to entities from these countries to invest in India without prior approval</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/government-eases-fdi-norms-for-china-other-countries-sharing-land-border-with-india-sources/article70726047.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Centre invokes Essential Commodities Act to prioritise natural gas allocation to certain sectors</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>The Centre invokes Essential Commodities Act to prioritize natural gas allocation to certain sectors due to disruption of LNG shipments through the Strait of Hormuz.</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>India's natural gas consumption is 195 million metric standard cubic metres per day, with half of it being imported, The Ministry of Petroleum and Natural Gas has invoked the Essential Commodities Act to divert natural gas to priority sectors, The priority sectors include domestic piped natural gas, Compressed Natural Gas, Liquified Petroleum Gas production, fertilizer manufacturing, and tea industries</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Industry/centre-invokes-essential-commodities-act-to-prioritise-natural-gas-allocation-to-certain-sectors/article70725635.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Oil Ministry sets up panel as commercial LPG shortage hits hospitality sector</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Oil Ministry sets up panel to address commercial LPG shortage in hospitality sector due to Middle East conflict disrupting fuel lifelines.</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>India consumes 31.3 million tonnes of LPG annually, with 87% in domestic sector and 13% in commercial establishments, 62% of LPG requirement is met through imports, Strait of Hormuz shutdown affects 85-90% of India's LPG imports</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/oil-ministry-sets-up-panel-as-commercial-lpg-shortage-hits-hospitality-sector/article70725110.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>India will not raise petrol prices despite global crude headwinds: Government sources</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>India decides not to increase petrol prices despite rising global crude oil prices.</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>India will not raise petrol prices despite global crude headwinds, Benchmark crude oil prices breaching $100 per barrel, OMCs have enough cushion and are financially comfortable</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/india-will-not-raise-petrol-prices-despite-global-crude-headwinds-government-sources/article70723329.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Iran conflict forces Asian central banks into sharp policy rethink</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>Escalating West Asia crisis forces Asian central banks to rethink their policies, balancing growth and inflation concerns.</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>Escalating crisis in West Asia has changed the outlook for Asian central banks, Central banks face trade-off between supporting growth and countering inflation, Reserve Bank of India may focus on supporting growth by keeping interest rates low</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/iran-conflict-forces-asian-central-banks-into-sharp-policy-rethink/article70721801.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>U.S. urged India to buy Russian oil already at sea to ease supply fears: Energy Secretary Chris Wright</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>US Energy Secretary urges India to buy Russian oil already at sea to ease supply fears and stabilise the market.</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>US urged India to buy Russian oil already at sea to ease supply fears, Energy Secretary Chris Wright spoke to Indian authorities about buying Russian crude cargoes, Move is a short-term, pragmatic effort to stabilise the market</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/us-urged-india-to-buy-russian-oil-already-at-sea-to-ease-supply-fears-energy-secretary/article70721339.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Can loss calibrate expectation?</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Economy</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>Investment losses can have a positive impact on financial wellbeing by moderating expectations and reducing the dopamine effect.</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>Investment losses can improve financial wellbeing by moderating expectations, Relative wealth is the reference point driving desire, not absolute wealth, Experiencing realised and unrealised losses helps in moderating investment expectations</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Economy/can-loss-calibrate-expectation/article70718025.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>The Rearview Podcast | PC Mahalanobis: India’s First Data Cruncher</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>PC Mahalanobis, a Bengali statistician, made significant contributions to Indian statistical practice and economic planning.</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>PC Mahalanobis founded the Indian Statistical Institute in 1931, He shaped Indian statistical practice across sampling, agricultural experiments, and economic planning, He exercised powerful influence over the National Sample Survey and the Planning Commission</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/podcast/the-rearview-podcast-pc-mahalanobis-indias-first-data-cruncher/article70730811.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>What is cheaper to cook with, LPG or induction?</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>The article compares the cost-effectiveness of LPG and induction stoves, highlighting the efficiency and lower costs of induction stoves.</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>LPG cylinders are in short supply and expensive, with a non-subsidised LPG cylinder costing ₹913 in cities like Delhi, Induction stoves are more efficient and cost-effective compared to LPG, Induction stoves generate heat directly in the vessel instead of the stovetop, reducing heat loss</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/science/what-is-cheaper-to-cook-with-lpg-or-induction/article70727929.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>India’s Project Cheetah must stop importing big cats, say scientists</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>India's Project Cheetah aims to introduce African cheetahs to India for global conservation and improve livelihood options for local communities.</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Project Cheetah aims to introduce African cheetahs to India for global conservation, The scheme also hopes to improve livelihood options for local communities through ecotourism, India now has 53 cheetahs, including 33 cubs born in India and 20 adults brought from Namibia and South Africa</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/energy-and-environment/project-cheetah-must-stop-importing-big-cats-say-scientists/article70718538.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>HALEU-Thorium fuel unsuitable for Indian nuclear reactors: study</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>India's HALEU-Thorium fuel is not compatible with its nuclear reactors, affecting its long-term nuclear energy plan.</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>India has vast thorium reserves but HALEU-Thorium fuel is unsuitable for Indian nuclear reactors, ANEEL fuel is being explored by NTPC and Clean Core Thorium Energy, SHANTI Act allows private companies to deploy advanced technologies</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/science/haleu-thorium-fuel-unsuitable-for-indian-nuclear-reactors-study/article70718796.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ISRO and ESA sign agreement for Earth Observation missions</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>ISRO and ESA sign agreement for Earth Observation missions, highlighting long-term cooperation and upcoming opportunities in space research.</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>ISRO and ESA signed an agreement for Earth Observation missions, Long-term cooperation between ISRO and ESA since 1978 and renewed in 2002, Agreement focuses on joint calibration and validation activities and scientific studies for Earth Observation Missions</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/science/isro-and-esa-sign-agreement-for-earth-observation-missions/article70719746.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Global warming picking up pace, study says</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Science</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>A new study confirms that global warming has entered a phase of significant acceleration, with the earth warming faster over the last decade than any other decade on record.</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>Global warming has accelerated with a shift becoming statistically significant around the year 2015, The earth has warmed faster over the last decade than during any other decade on record, The cause is likely a drop in aerosol levels due to countries cleaning up air pollution</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/science/global-warming-picking-up-pace-study-says/article70718501.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Women riders from the Northeast champion a cleaner Himalayas</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Eight women riders from Northeast India embark on a journey to promote eco-awareness and waste management in the Himalayas.</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>Himalayan Fringes Project aims to build waste-free mountain communities, Royal Enfield Social Mission and Further &amp; Beyond collaborate with Indian Army, Eight women riders from Northeast India promote eco-awareness and waste management</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/energy-and-environment/women-riders-from-the-northeast-champion-a-cleaner-himalayas/article70729387.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Committed to protecting the Aravalli hills, says  Bhupender Yadav</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>Union Minister Bhupender Yadav assures protection of Aravalli hills and mentions government's conservation efforts.</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>Union Government is committed to conserving the Aravalli ranges, Illegal mining in Aravalli hills was rampant during Ashok Gehlot's regime, Government has banned illegal mining in Delhi, Faridabad, and Gurugram</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/energy-and-environment/committed-to-protecting-the-aravalli-hills-says-bhupender-yadav/article70727866.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>MPs demand stricter enforcement of laws to tackle air pollution</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>MPs demand stricter enforcement of laws to tackle air pollution in Delhi and call for restructuring of the Environment Ministry to address climate change challenges.</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>Air pollution crisis in Delhi, Need for stricter enforcement of laws to curb pollution, Conceptual restructuring of Environment Ministry to meet climate change challenges</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/rajya-sabha-members-demand-stricter-law-enforcement-to-reduce-air-pollution/article70723132.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Cheetahs moving from Kuno to Rajasthan show ‘natural territorial behaviour’: NTCA</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>Cheetahs reintroduced in India are showing natural territorial behaviour by moving from Kuno National Park to Baran in Rajasthan.</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>Cheetahs from Kuno National Park in Madhya Pradesh are moving to Baran in Rajasthan, showing natural territorial behaviour, The cheetahs are being tracked via satellite and are radio-collared, The movement is part of the Project Cheetah Action Plan, which anticipates inter-State movement within the Kuno–Gandhi Sagar metapopulation landscape</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/energy-and-environment/cheetahs-moving-from-kuno-to-rajasthan-show-natural-territorial-behaviour-ntca/article70718922.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>What is the state of the environment in India? | Explained</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>India is facing severe environmental challenges, including extreme weather events, air pollution, and climate change, according to the Centre for Science and Environment's report.</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>India is facing the highest increase in frequency and impact of extreme weather events in 2025, with 99% of days affected, resulting in 4,419 reported deaths and affecting 17.41 million hectares of crop area., The climate crisis is reaching a point of no return, with the world expected to exceed 1.5 °C for the first time, according to the Centre for Science and Environment (CSE) report., The report highlights the need for nature-based solutions to address environmental challenges in India., Extreme weather events in India have been increasing in frequency and impact over the last four years.</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/sci-tech/energy-and-environment/what-is-the-state-of-the-environment-in-india-explained/article70717029.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Trapped in toxicity: Residents of Visakhapatnam’s Gajuwaka struggle for breath of fresh air</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Environment</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>Residents of Visakhapatnam's Gajuwaka struggle with pollution due to a poorly managed garbage transfer station.</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>Garbage Transfer Station in Gajuwaka is a major source of pollution in Visakhapatnam, The facility receives hundreds of tonnes of waste daily, Waste is transported to Kapuluppada, the city's main dumping site</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/Visakhapatnam/trapped-in-toxicity-visakhapatnam-residents-struggle-for-breath-of-fresh-air/article70707520.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Reports of ‘captive’ civilians spark fresh Naga-Kuki tensions in Manipur’s Ukhrul</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Tensions escalate in Manipur's Ukhrul district between Naga and Kuki communities, prompting government intervention</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>Tensions between Naga and Kuki communities in Manipur's Ukhrul district, Manipur Chief Minister Yumnam Khemchand Singh appeals for safe release of civilians, Government monitoring situation and promising strict action against those involved</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/reports-of-captive-civilians-spark-fresh-naga-kuki-tensions-in-manipurs-ukhrul-10577115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>West Asia crisis a reminder for self-reliance, energy growth: PM Modi</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi emphasizes the need for self-reliance in energy sector amidst West Asia crisis.</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>Importance of self-reliance in energy sector, Expansion of petroleum sector, Need for atmanirbhar Bharat</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/west-asia-crisis-energy-self-reliance-pm-modi-kerala-speech-10576999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Amid LPG worries, note of caution from Goa hotels body: ‘F&amp;B businesses could be hit’</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Goa hotels body warns of potential LPG shortage crisis affecting tourism and economy.</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage due to West Asia conflict, Impact on food and beverage establishments and hotels in Goa, Potential crisis for tourism and ancillary businesses</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/lpg-worries-goa-hotels-body-fb-businesses-hit-10576942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>‘We don’t abandon our own’: PM Modi cites rescue of nurses and Father Tom to slam Congress in Kerala</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi criticizes Congress for playing politics over crisis in West Asia, highlights BJP-NDA government's rescue efforts.</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>Government's efforts to ensure safety of Indians in crisis-hit regions, PM Modi's statement on BJP-NDA government's rescue operations, Comparison with previous government (Congress)</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/pm-modi-congress-politics-west-asia-tensions-nda-rally-kerala-10576348/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Two Indians killed, one missing in merchant vessels attack amid Israel-US Iran war: MEA</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Two Indians killed and one missing in merchant vessels attack amid Israel-US Iran war, affecting India's trade and economy</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>India's trade with the Gulf region is worth USD 200 billion annually, Significant investments from the Gulf region into the Indian economy in the last decade, Supply chain disruptions and instability in the Gulf region affecting Indian economy</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/indians-killed-missing-merchant-vessels-attack-israel-is-iran-war-10576776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>108 Maoists, Rs 3.6 crore cash, 1 kg gold – surrenders mark days leading up to Home Ministry deadline</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>108 Maoists, including 44 women, surrendered in Bastar, returning significant amounts of cash and weapons, ahead of the Home Ministry's deadline to eradicate Left Wing Extremism.</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>108 Maoists surrendered in Bastar, returning 101 weapons, Rs 3.61 crore in cash and 1 kg gold, Collective reward of Rs 3.29 crore for their capture, 2,714 Maoist cadres in Chhattisgarh have abandoned the path of violence over the past 26 months</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/108-maoists-cash-gold-surrenders-home-ministry-deadline-10576767/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>India LPG Gas Shortage Live Updates:  LPG shortage hits Pune’s Zomato, Swiggy food delivery partners</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>IEA releases 400 million barrels of oil to control crude prices</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>IEA agreed to release 400 million barrels of oil, Largest such move in IEA's history, 32 member countries backed the move</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/india-lpg-gas-shortage-live-updates-iran-israel-restaurants-petrol-pumps-10576531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>As Panaji votes for municipal polls today, what do voters most care about?</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - India</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>Panaji municipal polls highlight key concerns of voters including traffic congestion, waste management, and urbanisation issues.</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>Urbanisation and migration issues, Traffic congestion and parking woes, Waste management and drainage system problems</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/panaji-municipal-polls-traffic-tourism-key-voter-issues-10576465/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>LPG price hiked to balance consumer interest, oil cos’ finances; no plan to raise petrol, diesel prices: Govt sources</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>Government hikes LPG price to balance consumer interest and oil companies' finances, while assuring no increase in petrol and diesel prices.</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>LPG price hiked by Rs 60 per cylinder for domestic consumers, No plan to raise petrol and diesel prices despite global price surge, OMCs are financially well-positioned for petrol and diesel</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/lpg-price-hike-consumer-interest-oil-companies-raise-petrol-diesel-prices-10570219/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>‘Essential partner’: US gives India one-month waiver to buy Russia oil</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>US gives India a temporary waiver to buy Russian oil due to disruptions in oil imports through the Strait of Hormuz.</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>US issues 30-day waiver for India to buy Russian oil, India imports 88% of its oil needs, Strait of Hormuz effectively closed, affecting oil imports</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/essential-partner-us-gives-india-one-month-waiver-to-buy-russia-oil-10568907/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>India key driver of global growth: Shaktikanta Das</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Former RBI Governor Shaktikanta Das praises India's economic resilience and stability in the face of global economic challenges.</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>India is a model of prudence and stability in the global economy, India's approach to fiscal management is a key marker of its stability, IMF has noted risks to global growth outlook</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/india-key-driver-of-global-growth-shaktikanta-das-10558355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>US import duties on Indian solar panels may hit domestic OEMs</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>US imposes high import duties on Indian solar panels, potentially affecting domestic OEMs and solar project implementation in India.</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>US imposes 126% preliminary countervailing duties on Indian solar panel imports, India's solar module manufacturing capacity exceeds 140 GW per annum, Potential pricing pressures on domestic OEMs and impact on solar project implementation</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/us-import-duties-on-indian-solar-panels-may-hit-domestic-oems-10552550/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>New debt-GDP fiscal anchor will likely open space for higher capex</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Centre to present its ninth consecutive Budget with a new fiscal anchor, shifting from fiscal deficit to debt-GDP ratio.</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>Centre shifting from fiscal deficit to debt-GDP ratio as fiscal anchor, Projected debt-to-GDP ratio for FY27 is 55% of GDP, New anchor to provide flexibility to respond to economic shocks and maintain long-term sustainability</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/new-debt-gdp-fiscal-anchor-will-likely-open-space-for-higher-capex-10506159/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Economic Survey 2025-26: ‘Economic sobriety’ while ‘running the sprint and marathon together’</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>Economic Survey 2025-26 emphasizes the need for 'strategic sobriety' and 'running the sprint and marathon together' in a disrupted world.</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>India is on the cusp of becoming the world's third largest economy, External challenges include geopolitical conflicts and over-leveraged technology sector, India's manufacturing sector faces challenges due to upstream protectionism impacting MSME competitiveness</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/economic-survey-2025-26-economic-sobriety-while-running-the-sprint-and-marathon-together-10502421/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>UPI-like AI, credit-based fellowship for kids, caution for IT: Economic Survey on AI</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>Economic Survey 2025-26 proposes AI-OS initiative and sector-specific AI applications to promote AI development in India.</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>Economic Survey 2025-26 proposes AI-OS initiative for public AI infrastructure, Focus on sector-specific AI applications rather than large language models, Recommendation for credit-based fellowship for kids to participate in AI economy</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/upi-ai-credit-fellowship-kids-caution-tech-economic-survey-10501261/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Economic Survey flags drying up of FDI/FII flow, Re stability</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>The Economic Survey for 2025-26 highlights India's strong economic fundamentals but concerns about the drying up of FDI/FII flow and rupee stability.</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>India's economic growth rate is projected to be 6.8-7.2% in the next financial year, The rupee has weakened by almost 7% since the start of 2025 against the US dollar, India depends on foreign capital flows to maintain a healthy balance of payments</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/economic-survey-india-economy-2026-27-nirmala-sitharaman-fiscal-10501002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>After recovery optimism, early Q3 results point to headwinds</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>India's Q3 financial results show headwinds for IT and other sectors, despite RBI's rate cuts and growth in bank credit.</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>IT companies set aside over Rs 5,500 crore for Labour Codes implementation, Reliance Industries and ICICI Bank posted lower-than-expected earnings numbers, RBI lowered policy repo rate to 5.25% and growth in non-food bank credit rose to 11.4%</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/after-recovery-optimism-early-q3-results-point-to-headwinds-10485670/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>Fitch Ratings: ‘Indian earnings likely to improve in FY27, but US tariff cloud remains’</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>Fitch Ratings expects Indian corporates' financial performance to improve in FY27, driven by revenue growth and improved EBITDA margins.</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>Indian corporates' credit metrics expected to be stable in FY27, Expected 6% revenue growth in FY27 driven by steady GDP growth and improved consumer-spending outlook, EBITDA margin expected to improve to 16% in FY27</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/fitch-ratings-indian-earnings-likely-to-improve-in-fy27-but-us-tariff-cloud-remains-10485656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>India seeks easier access to EU steel scrap to soften carbon tax impact</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>India seeks easier access to EU steel scrap to soften the impact of EU's new carbon tax on Indian manufacturers.</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>India seeks easier access to EU steel scrap to soften carbon tax impact, EU's new import duty linked to carbon emissions restricts metal exports, India-EU free trade agreement (FTA) may be affected by EU's recycling policy</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/india-pushes-for-easier-access-to-european-unions-steel-scrap-10481745/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>GDP growth in FY26 expected at 7.4% despite US tariff troubles, show First Advanced Estimates</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>India's real GDP growth is expected to rise to 7.4% in FY26, despite US tariff troubles, according to the government's first advance estimate.</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>India's real GDP growth expected to rise to 7.4% in FY26, Nominal GDP growth set to fall to a five-year low of 8%, Nominal GDP in 2025-26 seen at Rs 357 lakh crore, equivalent to $3.97 trillion</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/fy26-real-gdp-growth-seen-at-7-4-budget-prep-to-build-on-data-10460105/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Continued focus on macro fundamentals, reforms to enable economy to maintain high growth: RBI’s State of The Economy article</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>RBI's State of The Economy article highlights the importance of macroeconomic fundamentals and economic reforms for India's high growth momentum.</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>India's GDP grew at 8.2% in Q2 FY26, its fastest pace in six quarters, Domestic drivers, particularly private consumption demand, underpinned the pick-up in growth momentum, RBI emphasizes the need for sustained focus on macroeconomic fundamentals and economic reforms</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/continued-focus-on-macro-fundamentals-reforms-to-enable-economy-maintain-high-growth-rbis-state-of-economy-article-10433745/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Repo rate cut 25 bp to 5.25%; ‘rare Goldilocks period’, says RBI Governor</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Economy</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>RBI cuts repo rate by 25 bp to boost growth and ease borrowing costs.</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>Repo rate cut by 25 bp to 5.25%, RBI projects GDP growth for FY26 at 7.3%, Headline inflation forecast trimmed to 2%</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/business/economy/repo-rate-cut-25-bp-to-5-25-rare-goldilocks-period-says-rbi-governor-10405107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>‘No need to panic’, Oil Ministry says government measures led to 25% rise in LPG production</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Government measures led to a 25% increase in LPG production and ensured secure crude supply in India.</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>Government measures led to 25% increase in LPG production, Crude oil sourced from non-Strait of Hormuz routes, Government absorbed significant cost increase to protect consumers</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/no-need-to-panic-oil-ministry-says-government-measures-led-to-25-rise-in-lpg-production-11773230875359.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>Fitch: Indian OMCs, GAIL may face cash-flow pressure amid Iran tensions and oil price rise</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Fitch Ratings warns Indian OMCs and GAIL of potential cash flow issues due to supply disruptions and oil price rise, but Centre's support may mitigate the impact.</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>Indian OMCs and GAIL may face cash flow issues due to supply disruptions and oil price rise, Fitch Ratings expects GAIL's leverage to rise due to Middle East LNG disruption, Centre likely to balance OMCs' financial health with efforts to manage inflation and fiscal policy</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/fitch-indian-omcs-hpcl-bpcl-ioc-gail-face-cash-flow-pressure-us-israel-iran-tensions-oil-price-rise-strait-of-hormuz-11773221299103.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Oil rises 1%, stays below $90/bbl as IEA weighs strategic stock release</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>IEA considers releasing oil reserves to ease global crude prices</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>IEA considers largest release of oil reserves in history, IEA member countries hold over 1.2 billion barrels of public emergency oil stocks, IEA assesses global energy supply situation and market conditions</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/crude-oil-prices-iea-stock-reserve-release-india-imports-donald-trump-11773198209499.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>India’s farm output seen surging to record levels, buoyed by wheat</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>India's farm sector is expected to reach record levels in 2025-26 with projected foodgrain production.</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>India's farm sector is poised for a strong year with foodgrain production projected to reach record levels in 2025-26, Kharif foodgrain output is estimated at 174.14 million tonnes and rabi foodgrain production at 174.5 million tonnes, Wheat production is estimated at a record 120.2 million tonnes</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/india-foodgrain-production-record-second-advance-estimates-11773150955850.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Facing domestic cooking gas supply squeeze, Indian refiners up LPG production by 10%, secure 20 very large gas carriers</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Indian refiners increase LPG production and secure additional cargo to meet domestic demand amidst US-Iran war</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>Indian refiners increased LPG production by 10% due to supply squeeze from US-Iran war, 20 VLGCs carrying 1 million tonne cargo secured from the US and other countries, India still short of 20 VLGCs, with a total shortfall of 40 VLGCs</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/india-cooking-gas-supply-crisis-government-measures-refiners-boost-production-11773149662690.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Centre seeks Parliament nod for net extra spending of  ₹2 trillion in FY26 amid commodity price volatility</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>The Centre seeks Parliament's approval for ₹2 trillion in net additional spending in FY26 due to higher subsidies and defence expenditure.</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>Centre seeks Parliament nod for net extra spending of ₹2 trillion in FY26, Higher food and fertilizer subsidies, defence revenue expenditure and transfers to reserve funds drive additional spending, Net additional cash outgo amounts to 0.6% of India's nominal GDP</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/centre-seeks-parliament-nod-for-net-extra-spending-of-rs-2-trillion-in-fy26-amid-commodity-price-volatility-11773144565700.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>SpiceJet Chairman warns of possible 'fuel surcharge' even if crude stays at around $90 amid West Asia tensions</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Indian airlines may face increased costs due to high crude oil prices, potentially leading to higher domestic fares.</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>Crude oil prices remain high, affecting Indian carriers, Airlines may introduce 'fuel surcharge' to pass on increased costs, Indian carriers are exposed to rising oil prices due to dependence on Gulf routes</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/spicejet-chairman-warns-of-possible-fuel-surcharge-even-if-crude-stays-at-around-90-amid-west-asia-tensions-11773135389411.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Retail inflation likely inched up to 3.1% in February: Mint poll</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Retail inflation in India is expected to rise to 3.1% in February, driven by increases in food prices, and is likely to reach RBI's medium-term target of 4%.</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>Retail inflation expected to rise to 3.1% in February, Food and beverages dominate the overall inflation basket, Inflation closer to RBI's medium-term target of 4%</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/retail-inflation-likely-inched-up-to-3-1-in-february-mint-poll-food-beverages-fuel-oil-consumer-spending-11773129753518.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>E-way bills point to slower yet robust economic activity in February</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>E-way bills indicate slower yet robust economic activity in February, with supply chain activity remaining resilient.</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>E-way bills dipped 3.1% in February from January, 132.5 million electronic permits were raised in February, Supply chain activity remains resilient and aligned with upward trajectory of past few years</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/india-e-way-bills-india-economic-activity-india-february-e-way-bills-supply-chain-consignments-ports-factories-retail-11773125110599.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>In charts: How the Iran war stacks up against previous oil shocks—and why it’s worse so far</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>The Iran war has led to a sharp rise in global oil prices, surpassing previous oil shocks since 1990, with Brent crude prices increasing by 39% within nine days of the initial strikes.</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>Iran war impact on global oil prices, Comparison with previous oil shocks since 1990, Sharp rise in Brent crude prices</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/iran-war-oil-shocks-west-asia-crisis-oil-supplies-brent-crude-market-strait-of-hormuz-11773123988151.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage: Check how much 14.2 kg cooking gas cylinder costs in your city — Delhi, Mumbai, Kolkata, Bengaluru</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>LPG prices hiked by ₹60 each due to supply issues linked to the conflict in West Asia, affecting India's economy.</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>LPG price hike by ₹60 each due to supply issues, India consumes 31.3 million tonnes of LPG annually with 62% imported, Disruptions in Strait of Hormuz affecting global oil and LNG trade</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/lpg-shortage-cylinder-price-hike-14-kg-cooking-gas-cost-in-your-city-delhi-mumbai-kolkata-bengaluru-chennai-hyderabad-11773117214607.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>US-Israel war with Iran sends oil soaring, raises alarms for India Inc</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>Livemint Economy</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>US-Israel war with Iran causes oil prices to surge, posing risks to Indian economy and companies.</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>US-Israel war with Iran sends crude prices soaring, Indian economy's heavy reliance on energy imports, Potential impact on Indian companies and consumer demand</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/economy/indian-companies-face-energy-import-cost-supply-chain-disruption-risks-11773066655439.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Centre reviews LPG supply situation with states, calls for tighter monitoring and security</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Centre reviews LPG supply situation with states, calls for tighter monitoring and security</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>LPG supply situation reviewed by Centre with states, Tighter monitoring and security called for, Possible implications on economy</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/centre-reviews-lpg-supply-situation-with-states-calls-for-tighter-monitoring-and-security/articleshow/129472138.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>'No need to panic': PM Modi urges calm on concerns over energy crisis, says nation will overcome it like Covid-19</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi urges calm on concerns over energy crisis, assures the nation will overcome it.</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>Energy crisis in the country, PM Modi's statement on overcoming it like Covid-19, Implications of the energy crisis on the nation's economy</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/no-need-to-panic-pm-modi-urges-calm-on-concerns-over-energy-crisis-says-nation-will-overcome-it-like-covid-19/articleshow/129471859.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>MEA condemns attack on India-bound Thai ship, says innocent lives lost in conflict 'unacceptable'</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>MEA condemns attack on India-bound Thai ship, criticizes loss of innocent lives in conflict.</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>MEA condemns attack on India-bound Thai ship, Innocent lives lost in conflict are unacceptable, Conflict likely to impact international relations</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/mea-condemns-attack-on-india-bound-thai-ship-says-innocent-lives-lost-in-conflict-unacceptable-middle-east-crisis/articleshow/129470542.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Middle East crisis: 2 Indians killed, 1 missing after merchant vessels attacked, says MEA</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>India reports casualties in a Middle East crisis involving merchant vessels.</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>2 Indians killed, 1 missing after merchant vessels attacked in the Middle East, MEA (Ministry of External Affairs) confirms the incident, Possible implications on India's foreign policy and relations with Middle Eastern countries</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/middle-east-crisis-2-indians-killed-1-missing-after-merchant-vessels-attacked-says-mea/articleshow/129466489.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>No-confidence motion against Lok Sabha Speaker Om Birla defeated by voice vote amid opposition protest</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>Lok Sabha Speaker Om Birla's no-confidence motion defeated by voice vote amidst opposition protest.</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>No-confidence motion against Lok Sabha Speaker Om Birla, Motion defeated by voice vote, Opposition protest</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/no-confidence-motion-against-lok-sabha-speaker-om-birla-defeated-by-voice-vote-amid-opposition-protest/articleshow/129464444.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Evening news wrap: IRCTC directs station kitchens to use microwave, induction; PM Modi assures help for Indians stranded in Gulf &amp;amp; more</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC directs station kitchens to use microwave and induction, PM Modi assures help for Indians stranded in Gulf.</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC directs station kitchens to use microwave, induction, PM Modi assures help for Indians stranded in Gulf, Possible implications of IRCTC's directive on food quality and economy</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/evening-news-wrap-irctc-directs-station-kitchens-to-use-microwave-induction-pm-modi-assures-help-for-indians-stranded-in-gulf-more/articleshow/129460302.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Arvind Kejriwal appeals to Delhi high court Chief Justice to transfer excise policy case to 'impartial' bench</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>Delhi CM Arvind Kejriwal appeals to transfer excise policy case to an impartial bench.</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>Arvind Kejriwal appeals to Delhi high court Chief Justice to transfer excise policy case, Impartial bench sought, Delhi excise policy case</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/arvind-kejriwal-appeals-to-delhi-high-court-chief-justice-to-transfer-excise-policy-case-to-impartial-bench/articleshow/129460381.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>9. Defense &amp; Security</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>AI Express flight from Hyd makes a hard landing at Phuket, gets stuck on runway; all safe</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>Air India Express flight experiences hard landing in Phuket, all passengers safe</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>Air India Express Boeing 737 MAX experienced a hard landing in Phuket, Nose wheels detached upon the second touchdown, Directorate General of Civil Aviation is investigating the incident</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/ai-express-flight-from-hyd-makes-a-hard-landing-at-phuket-gets-stuck-on-runway-all-safe/articleshow/129457161.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Aravallis lost 13.8% soil per year during 2017-2024: Study</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>A study reveals significant soil loss and land conversion in the Aravalli region, threatening its delicate ecosystem.</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>Soil loss in Aravallis increased by 13.8% annually from 2017-2024, Built-up areas surged 53% in the region, Massive land conversion due to human activity and climate change threatens the Aravalli mountain range</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/aravallis-lost-13-8-soil-per-year-during-2017-2024-study/articleshow/129454253.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Indian students in Iran begin arranging exit amid safety concerns; first batch set to depart for Armenia border</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Indian students in Iran are arranging their exit amid safety concerns, with the first batch set to depart for the Armenia border.</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>Indian students in Iran are arranging their exit due to safety concerns, First batch set to depart for Armenia border, Implications of the situation on India-Iran relations</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/indian-students-in-iran-begin-arranging-exit-amid-safety-concerns-first-batch-set-to-depart-for-armenia-border/articleshow/129453259.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>'All help will be given to Indians in Gulf': PM Modi assures in Kerala; attacks Congress for 'politicising' issue</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>Times of India</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi assures help to Indians in Gulf, criticizes Congress for politicizing the issue.</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi assures help to Indians in Gulf, Congress accused of politicising the issue, Economic implications of Indians in Gulf</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/all-help-will-be-given-to-indians-in-gulf-pm-modi-assures-in-kerala-attacks-congress-for-politicising-issue/articleshow/129451714.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Private hostels start using firewood to prepare meals for the students</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Private hostels in Karnataka are facing a commercial LPG shortage, leading them to switch to alternative fuel sources like firewood.</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>Commercial LPG shortage affecting private hostels and educational institutions, Private hostels switching to alternative fuel sources like firewood, Government-run hostels not facing problems due to domestic LPG supply</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/private-hostels-start-using-firewood-to-prepare-meals-for-the-students/article70732128.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru: LPG shortage hits prasada preparation in some temples</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage hits prasada preparation in some temples in Karnataka, prompting government intervention</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage affects temple prasada preparation, 15 major temples in Karnataka facing difficulties, Government monitoring the situation and considering steps to reduce fuel consumption</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/bengaluru-lpg-shortage-hits-prasada-preparation-in-some-temples/article70731913.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Bangalore varsity conducts online exams for distance education students for the first time</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Bangalore University conducted its first-ever online examination for distance education students, following UGC guidelines.</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>University Grants Commission (UGC) has guidelines for online exams, Bangalore University conducted online exams for distance education students, Advanced artificial intelligence-based tools used for monitoring the examination process</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/bangalore-varsity-conducts-online-exams-for-distance-education-students-for-the-first-time/article70731391.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court upholds conviction of former Mudigere MLA M.P. Kumaraswamy in cheque dishonour case</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court upholds conviction of former MLA M.P. Kumaraswamy in cheque dishonour case, orders him to pay ₹1.23 crore to the complainant.</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka High Court upholds conviction of former MLA M.P. Kumaraswamy in cheque dishonour case, Total amount to be paid to the complainant is ₹1.23 crore, Failure to pay will result in simple imprisonment of six months in each case</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/karnataka-high-court-upholds-conviction-of-former-mudigere-mla-mp-kumaraswamy-in-cheque-dishonour-case/article70731910.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Environment &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Dharwad residents stop lorries carrying garbage in protest</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Residents in Dharwad protest against municipal authorities' inaction over a garbage dumping yard fire, affecting door-to-door garbage collection.</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>Garbage dumping yard fire in Dharwad, Karnataka, causing smoke and health concerns, Residents protesting against municipal authorities' apathy, Door-to-door garbage collection affected, leading to dumping of waste on vacant land and roadside</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/dharwad-residents-stop-lorries-carrying-garbage-in-protest/article70731991.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru needs 1,074 km of new roads in four years: SFC report</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru requires 1,074 km of new roads over four years to address congestion, with a stagnant road network and increasing vehicle numbers.</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru needs 1,074 km of new roads in four years, Current road network is 13,000 km, stagnant for over a decade, Number of vehicles has doubled in the last decade, reaching 1.3 crore</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/bangalore/bengaluru-needs-1074-km-of-new-roads-in-four-years-sfc-report/article70731552.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Vanchit Bahujan Aghadi Party plans to expand presence in State</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Vanchit Bahujan Aghadi Party plans to expand its presence in the State ahead of zilla and taluk panchayat elections.</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>Vanchit Bahujan Aghadi Party plans to expand presence in the State, Party to form district and taluk committees to consolidate support at the grassroots level, Support for State Election Commission's move to hold panchayat elections with ballot papers rather than EVMs</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/vanchit-bahujan-aghadi-party-plans-to-expand-presence-in-state/article70727575.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Tobacco auctions halted again as farmers protest sharp fall in prices</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Tobacco farmers in Karnataka protest against sharp fall in prices due to tax burden and geopolitical tensions.</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>Tobacco prices declined due to excise duty and GST increase, Farmers protested against the price fall and tax burden, Geopolitical tensions may be affecting procurement</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/tobacco-auctions-halted-again-as-farmers-protest-sharp-fall-in-prices/article70731838.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Elector mapping exercise not being carried out properly, says BJP MLA</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>The Hindu - Karnataka</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>BJP MLA complains about improper conduct of elector mapping exercise in Belagavi district, citing low voter mapping rate and inefficient booth level officials.</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>Elector mapping exercise not being carried out properly in Belagavi district, Only 20% of names mapped in the last three months in Belagavi city, Booth level officials not doing their job properly</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/elector-mapping-exercise-not-being-carried-out-properly-says-bjp-mla/article70727423.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>LPG crisis: Karnataka minister Muniyappa assures monthly one cylinder per family, requests hotels to cooperate</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka minister assures monthly one LPG cylinder per family amid shortage triggered by Israel-Iran war</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>LPG shortage triggered by Israel-Iran war, India produces only 25-30% of its LPG requirement, Oil companies assured to deliver one cylinder per family per month</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/lpg-crisis-karnataka-minister-muniyappa-assures-monthly-one-cylinder-per-family-requests-hotels-to-cooperate-10576988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru prison security breach: Staff and visitor caught smuggling contraband</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>Prison authorities in Bengaluru foiled two separate attempts to smuggle prohibited items into the Parappana Agrahara Central Prison.</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>Prison security breach in Bengaluru, Staff and visitor caught smuggling contraband, Prison rules violated</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/bengaluru-prison-security-breach-smuggling-contraband-10576959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Idols, debris and decades of neglect: Bengaluru’s Ulsoor lake undergoes first full cleanup in 24 years</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru's Ulsoor lake undergoes first full cleanup in 24 years with a Rs 4-crore grant from NDMF and Rs 100 crore restoration work from BCCC.</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>National Disaster Mitigation Fund (NDMF) grant of Rs 4 crore for desilting the lake, Bengaluru Central City Corporation (BCCC) restoration work worth Rs 100 crore, BCCC's plan to complete desilting process before the monsoon</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/idols-debris-and-decades-of-neglect-bengalurus-ulsoor-lake-undergoes-first-full-cleanup-in-24-years-10576928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>‘5 questions on ChatGPT will use up half a litre of water’: Karnataka minister Priyank Kharge calls for sustainable data centres</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka government plans to frame a sustainable data centre policy to reduce water and energy consumption by data centres.</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>Data centres require 25 million litres of water annually for 1 MW capacity, Karnataka government to frame a sustainable data centre policy, Use of treated water and liquid cooling to reduce water demand</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/5-questions-on-chatgpt-will-use-up-half-a-litre-of-water-karnataka-minister-priyank-kharge-calls-for-sustainable-data-centres-10576852/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Mangaluru duo arrested for routing global cyberfraud millions through 70 local mule accounts</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka Police dismantle a 'crypto-as-a-service' network operating out of Mangaluru, arresting two men for facilitating international cyberfraud.</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>Use of 'crypto-as-a-service' network for international cyberfraud, Recruitment of local residents for mule accounts, Link to 88 cyberfraud complaints across the country</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/mangaluru-cyberfraud-crypto-service-mule-accounts-arrest-10576609/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Traffic signals go dark in Bengaluru’s Electronics City as UPS batteries stolen again</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>UPS batteries used to power traffic signals and streetlights were stolen in Bengaluru's Electronics City area, highlighting lapses in monitoring and maintenance of public infrastructure.</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro (L&amp;T) is responsible for maintaining the traffic infrastructure, UPS batteries were stolen from Bengaluru's Electronics City area, A case has been registered and an investigation is underway</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/traffic-signals-electronics-city-ups-batteries-stolen-again-10576527/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>Know Your City: From hosting Queen Elizabeth to reviving lost saris, how Chimy Nanjappa shaped Karnataka’s craft heritage</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>Chimy Nanjappa's efforts transformed the Cauvery Handicrafts Emporium into a showcase of Karnataka's finest crafts.</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>Cauvery Handicrafts Emporium is a state-owned emporium, Chimy Nanjappa worked to transform the emporium into a showcase of Karnataka's finest creations, Emporium was initially known as Mysore Arts and Crafts Emporium</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/know-your-city-from-hosting-queen-elizabeth-to-reviving-lost-saris-how-chimy-nanjappa-shaped-karnatakas-craft-heritage-10576299/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Government Schemes</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka government doctors call off planned stir after state agrees to meet 13 of 14 demands</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka government doctors call off strike after state agrees to meet 13 of 14 demands</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka government agreed to meet 13 of 14 demands of Karnataka Government Medical Officers' Association, Demands included amendments to Cadre and Recruitment Rules, filling vacancies, and appointment of a technical person as additional secretary, Association called off indefinite strike after government's assurance</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/karnataka-government-doctors-strike-called-off-demands-10576252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>Commercial LPG shortage in Bengaluru: Siddaramaiah urges Petroleum Minister Hardeep Puri to ensure adequate supply for eateries</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka CM Siddaramaiah appeals to Petroleum Minister to address commercial LPG shortage in Bengaluru due to Centre's directive.</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>Commercial LPG shortage in Bengaluru due to Centre's directive prioritizing domestic LPG supplies, Karnataka CM Siddaramaiah urges Petroleum Minister Hardeep Puri to ensure adequate commercial LPG supply, Shortage affects hospitality and food services sector in Bengaluru</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/siddaramaiah-hardeep-puri-commercial-lpg-shortage-west-asia-war-10576079/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>CID to probe Anekal realtor’s abduction and murder: Karnataka Home Minister G Parameshwara</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka Home Minister directs CID to probe abduction and murder case</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka Home Minister G Parameshwara directed the CID to take over the probe into the abduction and killing of a real estate businessman, One person has been arrested, and the search is on for others, The investigation will be carried out by the CID</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/anekal-businessman-murder-cid-probe-karnataka-10575949/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>EMI option for property tax in Bengaluru: New proposal aims to simplify payment</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>The State Finance Commission proposes an EMI scheme for property tax payments in Bengaluru to increase collection efficiency and incentivize timely payments.</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>Property tax EMI scheme proposed for Bengaluru to increase collection efficiency, 5% rebate for timely payment of property tax, Unassessed properties to add approximately Rs 1,000 crore annually to property tax revenue</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/bengaluru-property-tax-emi-scheme-sfc-recommendations-gba-10575160/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Rs 3-crore heist in Bengaluru: 19-year-old arrested in Rajasthan for stealing 1.8 kg of diamonds and gold from Yelahanka house</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>A 19-year-old man was arrested for stealing Rs 3 crore worth of diamonds and gold from a house in Bengaluru, highlighting the importance of technical intelligence in crime investigation.</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>Value of stolen goods (Rs 3 crore), Weight of stolen diamonds and gold (1.833 kg), Importance of technical intelligence in crime investigation</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/rs-3-crore-heist-in-bengaluru-19-year-old-arrested-in-rajasthan-for-stealing-1-8-kg-of-diamonds-and-gold-from-yelahanka-house-10575117/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:11:35</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Social Issues</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>2 am delivery turns violent: Blinkit agent booked for assaulting customer in Bengaluru</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Indian Express - Bangalore</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>A delivery agent allegedly assaulted a customer in Bengaluru, leading to a police case being registered.</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>Assault case registered against Blinkit delivery agent for allegedly assaulting a customer in Bengaluru, Customer sustained fracture injuries near his eye and face in the assault, Police formed a special team to trace and apprehend the accused</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/bangalore/blinkit-agent-booked-assaulting-customer-bengaluru-10577015/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5057,7 +11121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5904,6 +11968,786 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>According to the Opposition, what is the reason behind moving the motion for removal of Speaker Om Birla?</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>To satisfy the ego of one person</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>To protect the fundamental rights of MPs</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>To prevent the Leader of Opposition from speaking in the House</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>To strengthen the Speaker's position</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>The Opposition claims that the motion was moved to protect the fundamental rights of MPs, even though they knew the numbers were not in their favour. This is evident from the statement of Congress MP K.C. Venugopal, who said that the no-confidence motion was introduced to protect the fundamental rights of MPs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>What is the stance of the Iranian national police chief towards anti-government protesters?</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>He views them as innocent civilians deserving of protection</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>He treats them as enemies and threatens to deal with them accordingly</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>He remains neutral and does not take a stance</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>He encourages them to continue protesting</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>The Iranian national police chief, Ahmad-Reza Radan, has explicitly stated that protesters who support the enemy will be treated as enemies and dealt with accordingly, indicating a confrontational stance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>What is the primary reason cited by Amit Shah for not allowing Rahul Gandhi to speak in Parliament during his foreign trips?</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's low attendance and participation in key debates</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Lok Sabha's lack of provision for video conferencing</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are a breach of parliamentary norms</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are a breach of national security</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Amit Shah specifically mentioned that the Lok Sabha has no provision for video conferencing, which is why Rahul Gandhi cannot speak from abroad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Which Article of the Constitution is being referred to by BJP MP Baburam Nishad for imposing President's Rule in West Bengal?</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Article 356</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Article 370</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Article 371</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Article 372</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Article 356 of the Indian Constitution deals with the imposition of President's Rule in a state, which is what the BJP MP is seeking to invoke in this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Who is the Chairperson of the Bharatiya Bhasha Samiti constituted by the Education Ministry for promotion of Indian languages?</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Prof Michel Danino</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Sanyal</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Chamu Krishna Shastri</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Sudha Murty</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>According to the news, Chamu Krishna Shastri is the chairperson of the Bharatiya Bhasha Samiti constituted by the Education Ministry for promotion of Indian languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>According to the report, what was the primary reason for the US missile strike on the Iranian school?</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>The US military intentionally targeted the school as a retaliatory measure.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>The strike was a result of a cyber attack on the US military's targeting system.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>A targeting mistake led to the strike, as the school building was mistakenly identified as an adjacent Iranian base.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>The strike was a result of a miscalculation by the Iranian military.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>The correct answer is C, as the report states that the investigation found a targeting mistake to be the primary reason for the strike, with the school building being mistakenly identified as an adjacent Iranian base due to outdated data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>What was the outcome of the air strike that injured Mojtaba Khamenei, according to the news?</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Only Mojtaba Khamenei was injured</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Several members of the Khamenei family were killed</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>The air strike had no casualties</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>The strike only damaged the compound</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>The news states that the air strike also killed other members of the Khamenei family, including Mojtaba's wife and mother, which indicates that several members of the family were killed in the strike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>What is a likely consequence of a weak Opposition in Nepal's Parliament?</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Increased accountability of the government</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Improved parliamentary deliberations</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>The government may act waywardly and take wilful decisions</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Reduced polarization in politics</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>According to Chandrakishore, a political commentator, a weak Opposition in Parliament may lead to the government acting waywardly and taking wilful decisions, which could test democratic norms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>What is one of the goals of Russia's special military operation in Ukraine, as stated by the Kremlin?</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>To negotiate a ceasefire</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>To establish a buffer zone</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>To demilitarize Ukraine</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>To provide humanitarian aid</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>The Kremlin stated that one of the goals of the special military operation is to demilitarize Ukraine, in order to prevent barbaric actions by the Kyiv regime from continuing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Which of the following best describes the nature of governance as per PM Modi's statement about DMK?</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Merit-based governance</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Dynastic rule</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Participatory governance</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Decentralized governance</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>PM Modi's statement that 'everything starts and ends with one family' in DMK rule, and that 'power remains with only one dynasty' suggests that the governance is based on dynastic rule rather than merit or participation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Social Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Which of the following best describes the Kurumba painting art form?</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>A 2000-year-old art form originating from the Nilgiris</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>A 3000-year-old prehistoric art form</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>A modern art form popularized in the Nilgiris</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>A folk art form practiced in the southern states of India</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>The article states that Kurumba painting is a prehistoric art form, estimated to be over 3000 years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Which party received the highest number of votes under the proportional representation category in Nepal's general elections?</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Rastriya Swatantra Party (RSP)</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Nepali Congress</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>CPN-UML</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Nepali Communist Party</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>According to the Election Commission, the Rastriya Swatantra Party (RSP) received the highest number of votes under the proportional representation category, with 51,57,130 votes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>International Relations</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>What was the outcome of the US military's strikes on the Iranian base, as per the report?</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>The strikes resulted in the destruction of the Iranian base, but no civilian casualties.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>The strikes were successful in targeting the intended Iranian military targets, but the school was mistakenly hit.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>The strikes resulted in the killing of more than 150 people, mostly civilians, at an elementary school in Minab.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>The strikes were called off due to concerns over civilian casualties.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>The correct answer is C, as the report states that the strike on the elementary school in Minab killed more than 150 people, mostly civilians.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>How many members are elected through proportional representation in the House of Representatives (HoR) in Nepal?</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>The House of Representatives (HoR) in Nepal has a total of 275 seats, out of which 110 members are elected through proportional representation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>23:28:05</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Polity &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>What is a common pattern observed in Rahul Gandhi's foreign trips by Amit Shah?</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are only during summer vacations</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are only during Budget Sessions</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are only during Monsoon Sessions</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's foreign trips are only during Winter Sessions</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Amit Shah pointed out that Rahul Gandhi's foreign schedule coincides with important sessions like Budget Sessions, indicating a pattern of prioritizing foreign trips over parliamentary duties.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
